--- a/docs/downloads/04/tbl_other_act_all_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_marovoay_madiromiongana.xlsx
@@ -387,12 +387,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Commerçant, épicier, vendeur - Mpivarotra</t>
         </is>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Eleveur - Mpiompy</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -477,12 +459,6 @@
           <t>Exploitantforestier, bûcheron, charbonnier- Mpitrandraka ala, mpamaky kitay, mpanao arina</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +471,6 @@
           <t>Fournisseur de matières premières pour les matériaux de construction - Mpamatsy akora @ fanamboarana trano -</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -549,12 +519,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -598,12 +562,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -616,12 +574,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +586,6 @@
           <t>Animateur rural, alphabétiseur ? Mpanentana eny ambanivohitra, Mpampianatra mamaky teny sy manoratra</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,12 +598,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +610,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -688,12 +622,6 @@
           <t>Barman, serveur - Mpiasa @ trano fisotroana, mpandroso sakafo</t>
         </is>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +634,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -742,12 +664,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +676,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -796,12 +706,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,12 +718,6 @@
           <t>Démarcheur de bétail-Mpanao dabokandro</t>
         </is>
       </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -832,12 +730,6 @@
           <t>Démarcheur et Kinanga autre que produit de pêche - Mpanelanelana sy kinanga amin?ny vokatra hafa ankoatra ny jono</t>
         </is>
       </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -886,12 +778,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -922,12 +808,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -940,12 +820,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -958,12 +832,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -976,12 +844,6 @@
           <t>Exploitantforestier, bûcheron, charbonnier- Mpitrandraka ala, mpamaky kitay, mpanao arina</t>
         </is>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -994,12 +856,6 @@
           <t>Fournisseur de matières premières pour les matériaux de construction - Mpamatsy akora @ fanamboarana trano -</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1012,12 +868,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1066,12 +916,6 @@
           <t>Machiniste, ajusteur, tourneur, fraiseur, rectificateur, soudeur, mécanicien - Mpanao asa momba ny vy</t>
         </is>
       </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-      <c r="D40">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1084,12 +928,6 @@
           <t>Man?uvre ou ouvrier (entreprise et société) - ) - Mpanampy @ taotrano</t>
         </is>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1102,12 +940,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="D42">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1120,12 +952,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1138,12 +964,6 @@
           <t>Menuisier, charpentier, Ebéniste, Sculpteur - Mpandrafitra hazo, trano, Mpanao sary sokitra</t>
         </is>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1156,12 +976,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1192,12 +1006,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C47">
-        <v>3</v>
-      </c>
-      <c r="D47">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1210,12 +1018,6 @@
           <t>Piroguier - Mpivoy lakana</t>
         </is>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1228,12 +1030,6 @@
           <t>Porteur d'eau - Mpaka rano</t>
         </is>
       </c>
-      <c r="C49">
-        <v>2</v>
-      </c>
-      <c r="D49">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1246,12 +1042,6 @@
           <t>Producteur de toaka gasy, de betsa - Mpamboatra toaka gasy, betsa</t>
         </is>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1282,12 +1072,6 @@
           <t>Retraité - Misotro ronono, mandray fisotroan-dronono</t>
         </is>
       </c>
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1299,12 +1083,6 @@
         <is>
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
-      </c>
-      <c r="C53">
-        <v>2</v>
-      </c>
-      <c r="D53">
-        <v>0.1</v>
       </c>
     </row>
     <row r="54">
